--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CACERES PATRIMONIO DE LA HUMANIDAD.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CACERES PATRIMONIO DE LA HUMANIDAD.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1801</v>
+        <v>1.1207</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5984</v>
+        <v>3.8745</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.4182</v>
+        <v>-2.7537</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.5311</v>
+        <v>-3.5778</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6553</v>
+        <v>0.6713</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.1864</v>
+        <v>-4.2491</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1167</v>
+        <v>3.2701</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0473</v>
+        <v>1.1793</v>
       </c>
       <c r="L2" t="n">
-        <v>2.0693</v>
+        <v>2.0907</v>
       </c>
       <c r="M2" t="n">
-        <v>-6.6477</v>
+        <v>-6.8479</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.392</v>
+        <v>-0.508</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.2556</v>
+        <v>-6.3398</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8678</v>
+        <v>2.8344</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3613</v>
+        <v>4.2942</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7577</v>
+        <v>2.7833</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6036</v>
+        <v>1.5109</v>
       </c>
       <c r="V2" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8453</v>
+        <v>2.8823</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4443</v>
+        <v>-0.4572</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8028</v>
+        <v>1.9294</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2471</v>
+        <v>-2.3867</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.03559999999999999</v>
+        <v>-0.1002</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3019</v>
+        <v>2.2747</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.3376</v>
+        <v>-2.3748</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0858</v>
+        <v>3.1225</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8882</v>
+        <v>2.9237</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1975</v>
+        <v>0.1988</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.1214</v>
+        <v>-3.2228</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5863</v>
+        <v>-0.6492</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.5351</v>
+        <v>-2.5736</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.4581</v>
+        <v>-2.4295</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.0969</v>
+        <v>-4.0491</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.06960000000000002</v>
+        <v>-0.05709999999999998</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4528</v>
+        <v>0.4754</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5224</v>
+        <v>-0.5326</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1191</v>
+        <v>2.1295</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="4">
@@ -721,22 +721,22 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5692</v>
+        <v>-0.5813</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4382</v>
+        <v>-0.4533</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7068</v>
+        <v>-0.7158</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0793</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7903</v>
+        <v>-0.7951</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7068</v>
+        <v>-0.7158</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0793</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7903</v>
+        <v>-0.7951</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1375</v>
+        <v>0.1345</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2685</v>
+        <v>0.2625</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4075</v>
+        <v>-1.4088</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3582</v>
+        <v>2.4828</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.7658</v>
+        <v>-3.8917</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4077</v>
+        <v>0.4211</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9238</v>
+        <v>1.9553</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5161</v>
+        <v>-1.5341</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8401</v>
+        <v>3.9245</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0079</v>
+        <v>2.0723</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8322</v>
+        <v>1.8522</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.4325</v>
+        <v>-3.5033</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.08420000000000002</v>
+        <v>-0.1169</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.3483</v>
+        <v>-3.3864</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>1.229</v>
+        <v>1.2148</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9456</v>
+        <v>-0.9354</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.048</v>
+        <v>-1.0245</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1023</v>
+        <v>0.08909999999999998</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0744</v>
+        <v>-1.097</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6647</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.5219</v>
+        <v>-3.4314</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4484</v>
+        <v>1.7639</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.9702</v>
+        <v>-5.1953</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.0829</v>
+        <v>-6.0586</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9732</v>
+        <v>-1.9577</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.1097</v>
+        <v>-4.100899999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1144</v>
+        <v>-0.9252</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1911</v>
+        <v>-1.0734</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0766</v>
+        <v>0.1482</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.9684</v>
+        <v>-5.1334</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.782</v>
+        <v>-0.8843</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.1863</v>
+        <v>-4.2491</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4097000000000001</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R6" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0552</v>
+        <v>-1.0403</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4291</v>
+        <v>0.4631999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.4843</v>
+        <v>-1.5035</v>
       </c>
       <c r="V6" t="n">
-        <v>4.0259</v>
+        <v>4.0725</v>
       </c>
       <c r="W6" t="n">
-        <v>5.2065</v>
+        <v>5.2627</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.8887</v>
+        <v>-3.9146</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7423</v>
+        <v>-2.689</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1465</v>
+        <v>-1.2256</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.2936</v>
+        <v>-5.307700000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2216</v>
+        <v>-2.2331</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0718</v>
+        <v>-3.0745</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.6614</v>
+        <v>-2.6231</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9147</v>
+        <v>-1.8985</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7466999999999999</v>
+        <v>-0.7246000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.6321</v>
+        <v>-2.6846</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.307</v>
+        <v>-0.3347</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.3251</v>
+        <v>-2.3499</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3804999999999999</v>
+        <v>0.3808</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.08090000000000003</v>
+        <v>-0.06589999999999996</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4614</v>
+        <v>0.4467</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2673</v>
+        <v>-4.2664</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4914000000000001</v>
+        <v>0.7144000000000004</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.758599999999999</v>
+        <v>-4.9808</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.5817</v>
+        <v>-3.6319</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1043</v>
+        <v>2.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.686</v>
+        <v>-5.727600000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7733</v>
+        <v>0.8699</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9942</v>
+        <v>2.0716</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2209</v>
+        <v>-1.2016</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.354900000000001</v>
+        <v>-4.5018</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1102</v>
+        <v>0.0242</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.465</v>
+        <v>-4.5259</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0484</v>
+        <v>-2.0246</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0969</v>
+        <v>-4.0491</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6948</v>
+        <v>-1.6787</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9073</v>
+        <v>-0.8673000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7875000000000001</v>
+        <v>-0.8115</v>
       </c>
       <c r="V8" t="n">
-        <v>3.0577</v>
+        <v>3.0688</v>
       </c>
       <c r="W8" t="n">
-        <v>4.7224</v>
+        <v>4.7608</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6648</v>
+        <v>-1.692</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.0002</v>
+        <v>-8.998100000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6083</v>
+        <v>-1.3702</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.3919</v>
+        <v>-7.6279</v>
       </c>
       <c r="G9" t="n">
-        <v>-7.0841</v>
+        <v>-7.1102</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7531000000000001</v>
+        <v>-0.7888000000000002</v>
       </c>
       <c r="I9" t="n">
-        <v>-6.331</v>
+        <v>-6.3214</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4283</v>
+        <v>-0.2707000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8095000000000001</v>
+        <v>0.8855999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2378</v>
+        <v>-1.1564</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.6558</v>
+        <v>-6.8395</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5626</v>
+        <v>-1.6745</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.093</v>
+        <v>-5.165</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0484</v>
+        <v>-2.0246</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7728</v>
+        <v>-1.7462</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03620000000000001</v>
+        <v>0.07899999999999996</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.8088</v>
+        <v>-1.8252</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.758599999999999</v>
+        <v>-9.7135</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.7518</v>
+        <v>-7.5739</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0068</v>
+        <v>-2.1397</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.232900000000001</v>
+        <v>-5.2498</v>
       </c>
       <c r="H10" t="n">
-        <v>1.46</v>
+        <v>1.425</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.6929</v>
+        <v>-6.674799999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6327</v>
+        <v>-1.5502</v>
       </c>
       <c r="K10" t="n">
-        <v>1.9905</v>
+        <v>2.015</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.6233</v>
+        <v>-3.5653</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.6001</v>
+        <v>-3.6996</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5305000000000001</v>
+        <v>-0.5900000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.0696</v>
+        <v>-3.1096</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.4824</v>
+        <v>-3.4417</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0432</v>
+        <v>-1.0221</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9979</v>
+        <v>-0.9624</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.04540000000000002</v>
+        <v>-0.0597</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.868</v>
+        <v>-10.9121</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9142</v>
+        <v>-5.7957</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.953799999999999</v>
+        <v>-5.1165</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.440300000000001</v>
+        <v>-7.4882</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1887</v>
+        <v>-2.2315</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.2515</v>
+        <v>-5.2567</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.1136</v>
+        <v>-4.0442</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9088</v>
+        <v>-1.8793</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.2048</v>
+        <v>-2.1648</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3265</v>
+        <v>-3.444</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2799</v>
+        <v>-0.3521</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.0466</v>
+        <v>-3.0918</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3292</v>
+        <v>-1.3147</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2479</v>
+        <v>0.2730000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5771</v>
+        <v>-1.5877</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0744</v>
+        <v>-1.097</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0744</v>
+        <v>-1.097</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-42.5456</v>
+        <v>-42.5627</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.448399999999999</v>
+        <v>-6.7919</v>
       </c>
       <c r="F12" t="n">
-        <v>-34.0971</v>
+        <v>-35.7712</v>
       </c>
       <c r="G12" t="n">
-        <v>-38.5813</v>
+        <v>-38.81910000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3923</v>
+        <v>1.290300000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-39.9733</v>
+        <v>-40.109</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8654999999999999</v>
+        <v>1.773599999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>5.723</v>
+        <v>6.296300000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.8579</v>
+        <v>-4.522799999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-39.4462</v>
+        <v>-40.59270000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.3307</v>
+        <v>-5.0062</v>
       </c>
       <c r="O12" t="n">
-        <v>-35.1149</v>
+        <v>-35.5862</v>
       </c>
       <c r="P12" t="n">
-        <v>-10.2423</v>
+        <v>-10.1227</v>
       </c>
       <c r="Q12" t="n">
-        <v>-26.63</v>
+        <v>-26.319</v>
       </c>
       <c r="R12" t="n">
-        <v>16.3876</v>
+        <v>16.1964</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.031100000000001</v>
+        <v>-2.985</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7586000000000004</v>
+        <v>1.0257</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.7897</v>
+        <v>-4.011</v>
       </c>
       <c r="V12" t="n">
-        <v>9.309000000000001</v>
+        <v>9.363900000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>16.5581</v>
+        <v>16.7273</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.2493</v>
+        <v>-7.363300000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CACERES PATRIMONIO DE LA HUMANIDAD.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CACERES PATRIMONIO DE LA HUMANIDAD.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>P. UNIACKE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1207</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8745</v>
+        <v>-0.1281</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.7537</v>
+        <v>-0.5397</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.5778</v>
+        <v>-0.7158</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6713</v>
+        <v>0.0793</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.2491</v>
+        <v>-0.7951</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2701</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1793</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2.0907</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-6.8479</v>
+        <v>-0.7158</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.508</v>
+        <v>0.0793</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.3398</v>
+        <v>-0.7951</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.227</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.0613</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8344</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2942</v>
+        <v>0.048</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7833</v>
+        <v>-0.1281</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5109</v>
+        <v>0.1761</v>
       </c>
       <c r="V2" t="n">
-        <v>2.6313</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8823</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>L. PAUL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4572</v>
+        <v>-0.7104</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9294</v>
+        <v>3.0659</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3867</v>
+        <v>-3.7763</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1002</v>
+        <v>0.4211</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2747</v>
+        <v>1.9553</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.3748</v>
+        <v>-1.5341</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1225</v>
+        <v>3.9245</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9237</v>
+        <v>2.0723</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1988</v>
+        <v>1.8522</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.2228</v>
+        <v>-3.5033</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6492</v>
+        <v>-0.1169</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.5736</v>
+        <v>-3.3864</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.4295</v>
+        <v>0.2025</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.0491</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6196</v>
+        <v>1.2148</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.05709999999999998</v>
+        <v>-0.237</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4754</v>
+        <v>-0.4414</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5326</v>
+        <v>0.2043</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1295</v>
+        <v>-1.097</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3804</v>
+        <v>0.5951</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2509</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. UNIACKE</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5813</v>
+        <v>-1.0746</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1281</v>
+        <v>0.9951</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4533</v>
+        <v>-2.0697</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7158</v>
+        <v>-0.1002</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0793</v>
+        <v>2.2747</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7951</v>
+        <v>-2.3748</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3.1225</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2.9237</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.1988</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7158</v>
+        <v>-3.2228</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0793</v>
+        <v>-0.6492</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7951</v>
+        <v>-2.5736</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-2.4295</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.0491</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.6196</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1345</v>
+        <v>-0.6745000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1281</v>
+        <v>-0.4588</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2625</v>
+        <v>-0.2156</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.1295</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.3804</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. PAUL</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4088</v>
+        <v>-1.7951</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4828</v>
+        <v>2.2376</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.8917</v>
+        <v>-4.0328</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4211</v>
+        <v>-3.5778</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9553</v>
+        <v>0.6713</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5341</v>
+        <v>-4.2491</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9245</v>
+        <v>3.2701</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0723</v>
+        <v>1.1793</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8522</v>
+        <v>2.0907</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.5033</v>
+        <v>-6.8479</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1169</v>
+        <v>-0.508</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.3864</v>
+        <v>-6.3398</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2025</v>
+        <v>-2.227</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0123</v>
+        <v>-5.0613</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2148</v>
+        <v>2.8344</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9354</v>
+        <v>1.3783</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0245</v>
+        <v>1.1466</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08909999999999998</v>
+        <v>0.2317</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.097</v>
+        <v>2.6313</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5951</v>
+        <v>2.8823</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6921</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.4314</v>
+        <v>-2.489</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7639</v>
+        <v>1.9845</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.1953</v>
+        <v>-4.4735</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.0586</v>
+        <v>-3.6319</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9577</v>
+        <v>2.0958</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.100899999999999</v>
+        <v>-5.727600000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9252</v>
+        <v>0.8699</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.0734</v>
+        <v>2.0716</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1482</v>
+        <v>-1.2016</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.1334</v>
+        <v>-4.5018</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8843</v>
+        <v>0.0242</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.2491</v>
+        <v>-4.5259</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4049</v>
+        <v>-2.0246</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0368</v>
+        <v>-4.0491</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6319</v>
+        <v>2.0245</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0403</v>
+        <v>0.09870000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4631999999999999</v>
+        <v>0.4028</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5035</v>
+        <v>-0.3041</v>
       </c>
       <c r="V6" t="n">
-        <v>4.0725</v>
+        <v>3.0688</v>
       </c>
       <c r="W6" t="n">
-        <v>5.2627</v>
+        <v>4.7608</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1902</v>
+        <v>-1.692</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.9146</v>
+        <v>-2.5884</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.689</v>
+        <v>2.0997</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2256</v>
+        <v>-4.6879</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.307700000000001</v>
+        <v>-6.0586</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2331</v>
+        <v>-1.9577</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0745</v>
+        <v>-4.100899999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.6231</v>
+        <v>-0.9252</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8985</v>
+        <v>-1.0734</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7246000000000001</v>
+        <v>0.1482</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.6846</v>
+        <v>-5.1334</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3347</v>
+        <v>-0.8843</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.3499</v>
+        <v>-4.2491</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0123</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.0368</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0123</v>
+        <v>2.6319</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3808</v>
+        <v>-0.1973</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06589999999999996</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4467</v>
+        <v>-0.9962</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>4.0725</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>5.2627</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2664</v>
+        <v>-3.8857</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7144000000000004</v>
+        <v>-2.6891</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.9808</v>
+        <v>-1.1968</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.6319</v>
+        <v>-5.307700000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0958</v>
+        <v>-2.2331</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.727600000000001</v>
+        <v>-3.0745</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8699</v>
+        <v>-2.6231</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0716</v>
+        <v>-1.8985</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2016</v>
+        <v>-0.7246000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.5018</v>
+        <v>-2.6846</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0242</v>
+        <v>-0.3347</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.5259</v>
+        <v>-2.3499</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0246</v>
+        <v>1.0123</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0491</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0245</v>
+        <v>1.0123</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6787</v>
+        <v>0.4096000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8673000000000001</v>
+        <v>-0.066</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8115</v>
+        <v>0.4755</v>
       </c>
       <c r="V8" t="n">
-        <v>3.0688</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>4.7608</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.998100000000001</v>
+        <v>-8.022499999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3702</v>
+        <v>-0.9307999999999998</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.6279</v>
+        <v>-7.0917</v>
       </c>
       <c r="G9" t="n">
         <v>-7.1102</v>
@@ -1156,13 +1156,13 @@
         <v>2.227</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7462</v>
+        <v>-0.7705</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07899999999999996</v>
+        <v>0.5185</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.8252</v>
+        <v>-1.289</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3442</v>
@@ -1189,13 +1189,13 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.7135</v>
+        <v>-8.998699999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.5739</v>
+        <v>-7.2625</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1397</v>
+        <v>-1.7362</v>
       </c>
       <c r="G10" t="n">
         <v>-5.2498</v>
@@ -1234,13 +1234,13 @@
         <v>1.6196</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0221</v>
+        <v>-0.3072</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9624</v>
+        <v>-0.651</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0597</v>
+        <v>0.3438</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.9121</v>
+        <v>-10.306</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.7957</v>
+        <v>-5.524</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.1165</v>
+        <v>-4.7819</v>
       </c>
       <c r="G11" t="n">
         <v>-7.4882</v>
@@ -1312,13 +1312,13 @@
         <v>1.0123</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3147</v>
+        <v>-0.7085999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2730000000000001</v>
+        <v>0.5447</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5877</v>
+        <v>-1.2533</v>
       </c>
       <c r="V11" t="n">
         <v>-1.097</v>
@@ -1345,31 +1345,31 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-42.5627</v>
+        <v>-40.5382</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.7919</v>
+        <v>-6.151699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-35.7712</v>
+        <v>-34.3865</v>
       </c>
       <c r="G12" t="n">
-        <v>-38.81910000000001</v>
+        <v>-38.8191</v>
       </c>
       <c r="H12" t="n">
-        <v>1.290300000000001</v>
+        <v>1.2903</v>
       </c>
       <c r="I12" t="n">
         <v>-40.109</v>
       </c>
       <c r="J12" t="n">
-        <v>1.773599999999999</v>
+        <v>1.7736</v>
       </c>
       <c r="K12" t="n">
         <v>6.296300000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.522799999999999</v>
+        <v>-4.5228</v>
       </c>
       <c r="M12" t="n">
         <v>-40.59270000000001</v>
@@ -1390,16 +1390,16 @@
         <v>16.1964</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.985</v>
+        <v>-0.9605000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0257</v>
+        <v>1.6662</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.011</v>
+        <v>-2.6268</v>
       </c>
       <c r="V12" t="n">
-        <v>9.363900000000001</v>
+        <v>9.363899999999999</v>
       </c>
       <c r="W12" t="n">
         <v>16.7273</v>
